--- a/artfynd/A 32316-2022 artfynd.xlsx
+++ b/artfynd/A 32316-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117921676</v>
+        <v>117921669</v>
       </c>
       <c r="B2" t="n">
-        <v>78480</v>
+        <v>91772</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>761049</v>
+        <v>761245</v>
       </c>
       <c r="R2" t="n">
-        <v>7122378</v>
+        <v>7122347</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117921674</v>
+        <v>117921682</v>
       </c>
       <c r="B3" t="n">
-        <v>91772</v>
+        <v>78480</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>760966</v>
+        <v>761255</v>
       </c>
       <c r="R3" t="n">
-        <v>7122379</v>
+        <v>7122454</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117921684</v>
+        <v>117921683</v>
       </c>
       <c r="B4" t="n">
         <v>78480</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>761286</v>
+        <v>761278</v>
       </c>
       <c r="R4" t="n">
-        <v>7122485</v>
+        <v>7122476</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117921669</v>
+        <v>117921679</v>
       </c>
       <c r="B6" t="n">
-        <v>91772</v>
+        <v>91764</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>761245</v>
+        <v>761117</v>
       </c>
       <c r="R6" t="n">
-        <v>7122347</v>
+        <v>7122376</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117921673</v>
+        <v>117921672</v>
       </c>
       <c r="B7" t="n">
-        <v>78480</v>
+        <v>91784</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117921679</v>
+        <v>117921673</v>
       </c>
       <c r="B8" t="n">
-        <v>91764</v>
+        <v>78480</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4361</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>761117</v>
+        <v>760971</v>
       </c>
       <c r="R8" t="n">
-        <v>7122376</v>
+        <v>7122339</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,7 +1389,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117921683</v>
+        <v>117921684</v>
       </c>
       <c r="B9" t="n">
         <v>78480</v>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>761278</v>
+        <v>761286</v>
       </c>
       <c r="R9" t="n">
-        <v>7122476</v>
+        <v>7122485</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117921682</v>
+        <v>117921674</v>
       </c>
       <c r="B10" t="n">
-        <v>78480</v>
+        <v>91772</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>761255</v>
+        <v>760966</v>
       </c>
       <c r="R10" t="n">
-        <v>7122454</v>
+        <v>7122379</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117921672</v>
+        <v>117921676</v>
       </c>
       <c r="B11" t="n">
-        <v>91784</v>
+        <v>78480</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,25 +1605,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4366</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>760971</v>
+        <v>761049</v>
       </c>
       <c r="R11" t="n">
-        <v>7122339</v>
+        <v>7122378</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 32316-2022 artfynd.xlsx
+++ b/artfynd/A 32316-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117921669</v>
+        <v>117921672</v>
       </c>
       <c r="B2" t="n">
-        <v>91772</v>
+        <v>91786</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>761245</v>
+        <v>760971</v>
       </c>
       <c r="R2" t="n">
-        <v>7122347</v>
+        <v>7122339</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117921682</v>
+        <v>117921674</v>
       </c>
       <c r="B3" t="n">
-        <v>78480</v>
+        <v>91774</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>761255</v>
+        <v>760966</v>
       </c>
       <c r="R3" t="n">
-        <v>7122454</v>
+        <v>7122379</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117921683</v>
+        <v>117921669</v>
       </c>
       <c r="B4" t="n">
-        <v>78480</v>
+        <v>91774</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>761278</v>
+        <v>761245</v>
       </c>
       <c r="R4" t="n">
-        <v>7122476</v>
+        <v>7122347</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117921670</v>
+        <v>117921676</v>
       </c>
       <c r="B5" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>761244</v>
+        <v>761049</v>
       </c>
       <c r="R5" t="n">
-        <v>7122346</v>
+        <v>7122378</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117921679</v>
+        <v>117921682</v>
       </c>
       <c r="B6" t="n">
-        <v>91764</v>
+        <v>78482</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4361</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>761117</v>
+        <v>761255</v>
       </c>
       <c r="R6" t="n">
-        <v>7122376</v>
+        <v>7122454</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117921672</v>
+        <v>117921684</v>
       </c>
       <c r="B7" t="n">
-        <v>91784</v>
+        <v>78482</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4366</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>760971</v>
+        <v>761286</v>
       </c>
       <c r="R7" t="n">
-        <v>7122339</v>
+        <v>7122485</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117921673</v>
+        <v>117921677</v>
       </c>
       <c r="B8" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>760971</v>
+        <v>761068</v>
       </c>
       <c r="R8" t="n">
-        <v>7122339</v>
+        <v>7122379</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117921684</v>
+        <v>117921673</v>
       </c>
       <c r="B9" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>761286</v>
+        <v>760971</v>
       </c>
       <c r="R9" t="n">
-        <v>7122485</v>
+        <v>7122339</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117921674</v>
+        <v>117921670</v>
       </c>
       <c r="B10" t="n">
-        <v>91772</v>
+        <v>78482</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>760966</v>
+        <v>761244</v>
       </c>
       <c r="R10" t="n">
-        <v>7122379</v>
+        <v>7122346</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117921676</v>
+        <v>117921683</v>
       </c>
       <c r="B11" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>761049</v>
+        <v>761278</v>
       </c>
       <c r="R11" t="n">
-        <v>7122378</v>
+        <v>7122476</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117921677</v>
+        <v>117921679</v>
       </c>
       <c r="B12" t="n">
-        <v>78480</v>
+        <v>91766</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>4361</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>761068</v>
+        <v>761117</v>
       </c>
       <c r="R12" t="n">
-        <v>7122379</v>
+        <v>7122376</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 32316-2022 artfynd.xlsx
+++ b/artfynd/A 32316-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1795,6 +1795,924 @@
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>121568905</v>
+      </c>
+      <c r="B13" t="n">
+        <v>78608</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Gravmark, Vb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>761039</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7122413</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-07-19</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-07-19</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Linda Spjut</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Linda Spjut</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>121568906</v>
+      </c>
+      <c r="B14" t="n">
+        <v>78608</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Gravmark, Vb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>761042</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7122301</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-07-19</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-07-19</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Linda Spjut</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Linda Spjut</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>121568902</v>
+      </c>
+      <c r="B15" t="n">
+        <v>78608</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Gravmark, Vb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>761223</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7122416</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-07-19</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-07-19</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Linda Spjut</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Linda Spjut</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>121568903</v>
+      </c>
+      <c r="B16" t="n">
+        <v>56567</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Gravmark, Vb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>761213</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7122424</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-07-19</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-07-19</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Linda Spjut</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Linda Spjut</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>121568901</v>
+      </c>
+      <c r="B17" t="n">
+        <v>78608</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Gravmark, Vb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>761202</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7122373</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-07-19</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-07-19</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Linda Spjut</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Linda Spjut</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>121568900</v>
+      </c>
+      <c r="B18" t="n">
+        <v>78608</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Gravmark, Vb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>761216</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7122302</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-07-19</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-07-19</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Linda Spjut</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Linda Spjut</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>121569157</v>
+      </c>
+      <c r="B19" t="n">
+        <v>78608</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Gravmark, Vb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>761273</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7122339</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-07-03</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-07-03</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Linda Spjut</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Linda Spjut</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>121568907</v>
+      </c>
+      <c r="B20" t="n">
+        <v>78608</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Gravmark, Vb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>761060</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7122267</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-07-19</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-07-19</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Linda Spjut</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Linda Spjut</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>121568904</v>
+      </c>
+      <c r="B21" t="n">
+        <v>78608</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Gravmark, Vb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>761030</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7122463</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-07-19</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-07-19</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Linda Spjut</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Linda Spjut</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32316-2022 artfynd.xlsx
+++ b/artfynd/A 32316-2022 artfynd.xlsx
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121568905</v>
+        <v>121568903</v>
       </c>
       <c r="B13" t="n">
-        <v>78608</v>
+        <v>56568</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1809,25 +1809,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>761039</v>
+        <v>761213</v>
       </c>
       <c r="R13" t="n">
-        <v>7122413</v>
+        <v>7122424</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121568906</v>
+        <v>121568907</v>
       </c>
       <c r="B14" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>761042</v>
+        <v>761060</v>
       </c>
       <c r="R14" t="n">
-        <v>7122301</v>
+        <v>7122267</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2004,7 +2004,7 @@
         <v>121568902</v>
       </c>
       <c r="B15" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121568903</v>
+        <v>121569157</v>
       </c>
       <c r="B16" t="n">
-        <v>56567</v>
+        <v>78609</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2115,25 +2115,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>761213</v>
+        <v>761273</v>
       </c>
       <c r="R16" t="n">
-        <v>7122424</v>
+        <v>7122339</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2173,12 +2173,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121568901</v>
+        <v>121568904</v>
       </c>
       <c r="B17" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>761202</v>
+        <v>761030</v>
       </c>
       <c r="R17" t="n">
-        <v>7122373</v>
+        <v>7122463</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2310,7 +2310,7 @@
         <v>121568900</v>
       </c>
       <c r="B18" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2409,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121569157</v>
+        <v>121568906</v>
       </c>
       <c r="B19" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>761273</v>
+        <v>761042</v>
       </c>
       <c r="R19" t="n">
-        <v>7122339</v>
+        <v>7122301</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2479,12 +2479,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2511,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121568907</v>
+        <v>121568901</v>
       </c>
       <c r="B20" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>761060</v>
+        <v>761202</v>
       </c>
       <c r="R20" t="n">
-        <v>7122267</v>
+        <v>7122373</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2613,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121568904</v>
+        <v>121568905</v>
       </c>
       <c r="B21" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>761030</v>
+        <v>761039</v>
       </c>
       <c r="R21" t="n">
-        <v>7122463</v>
+        <v>7122413</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>

--- a/artfynd/A 32316-2022 artfynd.xlsx
+++ b/artfynd/A 32316-2022 artfynd.xlsx
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121568903</v>
+        <v>121569157</v>
       </c>
       <c r="B13" t="n">
-        <v>56568</v>
+        <v>78609</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1809,25 +1809,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>761213</v>
+        <v>761273</v>
       </c>
       <c r="R13" t="n">
-        <v>7122424</v>
+        <v>7122339</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121568907</v>
+        <v>121568903</v>
       </c>
       <c r="B14" t="n">
-        <v>78609</v>
+        <v>56568</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1911,25 +1911,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>761060</v>
+        <v>761213</v>
       </c>
       <c r="R14" t="n">
-        <v>7122267</v>
+        <v>7122424</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2001,7 +2001,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121568902</v>
+        <v>121568905</v>
       </c>
       <c r="B15" t="n">
         <v>78609</v>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>761223</v>
+        <v>761039</v>
       </c>
       <c r="R15" t="n">
-        <v>7122416</v>
+        <v>7122413</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2103,7 +2103,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121569157</v>
+        <v>121568907</v>
       </c>
       <c r="B16" t="n">
         <v>78609</v>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>761273</v>
+        <v>761060</v>
       </c>
       <c r="R16" t="n">
-        <v>7122339</v>
+        <v>7122267</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2173,12 +2173,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2205,7 +2205,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121568904</v>
+        <v>121568906</v>
       </c>
       <c r="B17" t="n">
         <v>78609</v>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>761030</v>
+        <v>761042</v>
       </c>
       <c r="R17" t="n">
-        <v>7122463</v>
+        <v>7122301</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2307,7 +2307,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121568900</v>
+        <v>121568902</v>
       </c>
       <c r="B18" t="n">
         <v>78609</v>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>761216</v>
+        <v>761223</v>
       </c>
       <c r="R18" t="n">
-        <v>7122302</v>
+        <v>7122416</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2409,7 +2409,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121568906</v>
+        <v>121568900</v>
       </c>
       <c r="B19" t="n">
         <v>78609</v>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>761042</v>
+        <v>761216</v>
       </c>
       <c r="R19" t="n">
-        <v>7122301</v>
+        <v>7122302</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2511,7 +2511,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121568901</v>
+        <v>121568904</v>
       </c>
       <c r="B20" t="n">
         <v>78609</v>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>761202</v>
+        <v>761030</v>
       </c>
       <c r="R20" t="n">
-        <v>7122373</v>
+        <v>7122463</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2613,7 +2613,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121568905</v>
+        <v>121568901</v>
       </c>
       <c r="B21" t="n">
         <v>78609</v>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>761039</v>
+        <v>761202</v>
       </c>
       <c r="R21" t="n">
-        <v>7122413</v>
+        <v>7122373</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>

--- a/artfynd/A 32316-2022 artfynd.xlsx
+++ b/artfynd/A 32316-2022 artfynd.xlsx
@@ -1797,7 +1797,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121569157</v>
+        <v>121568905</v>
       </c>
       <c r="B13" t="n">
         <v>78609</v>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>761273</v>
+        <v>761039</v>
       </c>
       <c r="R13" t="n">
-        <v>7122339</v>
+        <v>7122413</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121568903</v>
+        <v>121568901</v>
       </c>
       <c r="B14" t="n">
-        <v>56568</v>
+        <v>78609</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1911,25 +1911,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>761213</v>
+        <v>761202</v>
       </c>
       <c r="R14" t="n">
-        <v>7122424</v>
+        <v>7122373</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2001,7 +2001,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121568905</v>
+        <v>121568904</v>
       </c>
       <c r="B15" t="n">
         <v>78609</v>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>761039</v>
+        <v>761030</v>
       </c>
       <c r="R15" t="n">
-        <v>7122413</v>
+        <v>7122463</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2205,7 +2205,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121568906</v>
+        <v>121568902</v>
       </c>
       <c r="B17" t="n">
         <v>78609</v>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>761042</v>
+        <v>761223</v>
       </c>
       <c r="R17" t="n">
-        <v>7122301</v>
+        <v>7122416</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2307,7 +2307,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121568902</v>
+        <v>121568900</v>
       </c>
       <c r="B18" t="n">
         <v>78609</v>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>761223</v>
+        <v>761216</v>
       </c>
       <c r="R18" t="n">
-        <v>7122416</v>
+        <v>7122302</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2409,7 +2409,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121568900</v>
+        <v>121568906</v>
       </c>
       <c r="B19" t="n">
         <v>78609</v>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>761216</v>
+        <v>761042</v>
       </c>
       <c r="R19" t="n">
-        <v>7122302</v>
+        <v>7122301</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2511,7 +2511,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121568904</v>
+        <v>121569157</v>
       </c>
       <c r="B20" t="n">
         <v>78609</v>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>761030</v>
+        <v>761273</v>
       </c>
       <c r="R20" t="n">
-        <v>7122463</v>
+        <v>7122339</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2581,12 +2581,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2613,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121568901</v>
+        <v>121568903</v>
       </c>
       <c r="B21" t="n">
-        <v>78609</v>
+        <v>56568</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2625,25 +2625,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>761202</v>
+        <v>761213</v>
       </c>
       <c r="R21" t="n">
-        <v>7122373</v>
+        <v>7122424</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>

--- a/artfynd/A 32316-2022 artfynd.xlsx
+++ b/artfynd/A 32316-2022 artfynd.xlsx
@@ -1797,7 +1797,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121568905</v>
+        <v>121568904</v>
       </c>
       <c r="B13" t="n">
         <v>78609</v>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>761039</v>
+        <v>761030</v>
       </c>
       <c r="R13" t="n">
-        <v>7122413</v>
+        <v>7122463</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1899,7 +1899,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121568901</v>
+        <v>121568902</v>
       </c>
       <c r="B14" t="n">
         <v>78609</v>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>761202</v>
+        <v>761223</v>
       </c>
       <c r="R14" t="n">
-        <v>7122373</v>
+        <v>7122416</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2001,7 +2001,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121568904</v>
+        <v>121568907</v>
       </c>
       <c r="B15" t="n">
         <v>78609</v>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>761030</v>
+        <v>761060</v>
       </c>
       <c r="R15" t="n">
-        <v>7122463</v>
+        <v>7122267</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2103,7 +2103,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121568907</v>
+        <v>121568901</v>
       </c>
       <c r="B16" t="n">
         <v>78609</v>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>761060</v>
+        <v>761202</v>
       </c>
       <c r="R16" t="n">
-        <v>7122267</v>
+        <v>7122373</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121568902</v>
+        <v>121568903</v>
       </c>
       <c r="B17" t="n">
-        <v>78609</v>
+        <v>56568</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2217,25 +2217,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>761223</v>
+        <v>761213</v>
       </c>
       <c r="R17" t="n">
-        <v>7122416</v>
+        <v>7122424</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2307,7 +2307,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121568900</v>
+        <v>121568905</v>
       </c>
       <c r="B18" t="n">
         <v>78609</v>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>761216</v>
+        <v>761039</v>
       </c>
       <c r="R18" t="n">
-        <v>7122302</v>
+        <v>7122413</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2409,7 +2409,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121568906</v>
+        <v>121569157</v>
       </c>
       <c r="B19" t="n">
         <v>78609</v>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>761042</v>
+        <v>761273</v>
       </c>
       <c r="R19" t="n">
-        <v>7122301</v>
+        <v>7122339</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2479,12 +2479,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2511,7 +2511,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121569157</v>
+        <v>121568906</v>
       </c>
       <c r="B20" t="n">
         <v>78609</v>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>761273</v>
+        <v>761042</v>
       </c>
       <c r="R20" t="n">
-        <v>7122339</v>
+        <v>7122301</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2581,12 +2581,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2613,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121568903</v>
+        <v>121568900</v>
       </c>
       <c r="B21" t="n">
-        <v>56568</v>
+        <v>78609</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2625,25 +2625,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>761213</v>
+        <v>761216</v>
       </c>
       <c r="R21" t="n">
-        <v>7122424</v>
+        <v>7122302</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>

--- a/artfynd/A 32316-2022 artfynd.xlsx
+++ b/artfynd/A 32316-2022 artfynd.xlsx
@@ -1797,7 +1797,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121568902</v>
+        <v>121569157</v>
       </c>
       <c r="B13" t="n">
         <v>78616</v>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>761223</v>
+        <v>761273</v>
       </c>
       <c r="R13" t="n">
-        <v>7122416</v>
+        <v>7122339</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1899,7 +1899,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121568900</v>
+        <v>121568905</v>
       </c>
       <c r="B14" t="n">
         <v>78616</v>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>761216</v>
+        <v>761039</v>
       </c>
       <c r="R14" t="n">
-        <v>7122302</v>
+        <v>7122413</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121568904</v>
+        <v>121568903</v>
       </c>
       <c r="B15" t="n">
-        <v>78616</v>
+        <v>56569</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2013,25 +2013,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>761030</v>
+        <v>761213</v>
       </c>
       <c r="R15" t="n">
-        <v>7122463</v>
+        <v>7122424</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2103,7 +2103,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121569157</v>
+        <v>121568906</v>
       </c>
       <c r="B16" t="n">
         <v>78616</v>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>761273</v>
+        <v>761042</v>
       </c>
       <c r="R16" t="n">
-        <v>7122339</v>
+        <v>7122301</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2173,12 +2173,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2205,7 +2205,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121568906</v>
+        <v>121568901</v>
       </c>
       <c r="B17" t="n">
         <v>78616</v>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>761042</v>
+        <v>761202</v>
       </c>
       <c r="R17" t="n">
-        <v>7122301</v>
+        <v>7122373</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2307,7 +2307,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121568901</v>
+        <v>121568902</v>
       </c>
       <c r="B18" t="n">
         <v>78616</v>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>761202</v>
+        <v>761223</v>
       </c>
       <c r="R18" t="n">
-        <v>7122373</v>
+        <v>7122416</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2409,7 +2409,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121568907</v>
+        <v>121568900</v>
       </c>
       <c r="B19" t="n">
         <v>78616</v>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>761060</v>
+        <v>761216</v>
       </c>
       <c r="R19" t="n">
-        <v>7122267</v>
+        <v>7122302</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2511,7 +2511,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121568905</v>
+        <v>121568907</v>
       </c>
       <c r="B20" t="n">
         <v>78616</v>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>761039</v>
+        <v>761060</v>
       </c>
       <c r="R20" t="n">
-        <v>7122413</v>
+        <v>7122267</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2613,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121568903</v>
+        <v>121568904</v>
       </c>
       <c r="B21" t="n">
-        <v>56569</v>
+        <v>78616</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2625,25 +2625,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>761213</v>
+        <v>761030</v>
       </c>
       <c r="R21" t="n">
-        <v>7122424</v>
+        <v>7122463</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>

--- a/artfynd/A 32316-2022 artfynd.xlsx
+++ b/artfynd/A 32316-2022 artfynd.xlsx
@@ -1797,7 +1797,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121569157</v>
+        <v>121568901</v>
       </c>
       <c r="B13" t="n">
         <v>78616</v>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>761273</v>
+        <v>761202</v>
       </c>
       <c r="R13" t="n">
-        <v>7122339</v>
+        <v>7122373</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121568905</v>
+        <v>121568903</v>
       </c>
       <c r="B14" t="n">
-        <v>78616</v>
+        <v>56569</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1911,25 +1911,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>761039</v>
+        <v>761213</v>
       </c>
       <c r="R14" t="n">
-        <v>7122413</v>
+        <v>7122424</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121568903</v>
+        <v>121568904</v>
       </c>
       <c r="B15" t="n">
-        <v>56569</v>
+        <v>78616</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2013,25 +2013,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>761213</v>
+        <v>761030</v>
       </c>
       <c r="R15" t="n">
-        <v>7122424</v>
+        <v>7122463</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2205,7 +2205,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121568901</v>
+        <v>121568905</v>
       </c>
       <c r="B17" t="n">
         <v>78616</v>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>761202</v>
+        <v>761039</v>
       </c>
       <c r="R17" t="n">
-        <v>7122373</v>
+        <v>7122413</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2307,7 +2307,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121568902</v>
+        <v>121568907</v>
       </c>
       <c r="B18" t="n">
         <v>78616</v>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>761223</v>
+        <v>761060</v>
       </c>
       <c r="R18" t="n">
-        <v>7122416</v>
+        <v>7122267</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2409,7 +2409,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121568900</v>
+        <v>121568902</v>
       </c>
       <c r="B19" t="n">
         <v>78616</v>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>761216</v>
+        <v>761223</v>
       </c>
       <c r="R19" t="n">
-        <v>7122302</v>
+        <v>7122416</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2511,7 +2511,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121568907</v>
+        <v>121568900</v>
       </c>
       <c r="B20" t="n">
         <v>78616</v>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>761060</v>
+        <v>761216</v>
       </c>
       <c r="R20" t="n">
-        <v>7122267</v>
+        <v>7122302</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2613,7 +2613,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121568904</v>
+        <v>121569157</v>
       </c>
       <c r="B21" t="n">
         <v>78616</v>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>761030</v>
+        <v>761273</v>
       </c>
       <c r="R21" t="n">
-        <v>7122463</v>
+        <v>7122339</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2683,12 +2683,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 32316-2022 artfynd.xlsx
+++ b/artfynd/A 32316-2022 artfynd.xlsx
@@ -1797,7 +1797,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121568901</v>
+        <v>121568906</v>
       </c>
       <c r="B13" t="n">
         <v>78616</v>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>761202</v>
+        <v>761042</v>
       </c>
       <c r="R13" t="n">
-        <v>7122373</v>
+        <v>7122301</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121568903</v>
+        <v>121568900</v>
       </c>
       <c r="B14" t="n">
-        <v>56569</v>
+        <v>78616</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1911,25 +1911,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>761213</v>
+        <v>761216</v>
       </c>
       <c r="R14" t="n">
-        <v>7122424</v>
+        <v>7122302</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2001,7 +2001,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121568904</v>
+        <v>121568902</v>
       </c>
       <c r="B15" t="n">
         <v>78616</v>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>761030</v>
+        <v>761223</v>
       </c>
       <c r="R15" t="n">
-        <v>7122463</v>
+        <v>7122416</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2103,7 +2103,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121568906</v>
+        <v>121568904</v>
       </c>
       <c r="B16" t="n">
         <v>78616</v>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>761042</v>
+        <v>761030</v>
       </c>
       <c r="R16" t="n">
-        <v>7122301</v>
+        <v>7122463</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2205,7 +2205,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121568905</v>
+        <v>121568901</v>
       </c>
       <c r="B17" t="n">
         <v>78616</v>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>761039</v>
+        <v>761202</v>
       </c>
       <c r="R17" t="n">
-        <v>7122413</v>
+        <v>7122373</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2307,7 +2307,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121568907</v>
+        <v>121569157</v>
       </c>
       <c r="B18" t="n">
         <v>78616</v>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>761060</v>
+        <v>761273</v>
       </c>
       <c r="R18" t="n">
-        <v>7122267</v>
+        <v>7122339</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2377,12 +2377,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2409,7 +2409,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121568902</v>
+        <v>121568905</v>
       </c>
       <c r="B19" t="n">
         <v>78616</v>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>761223</v>
+        <v>761039</v>
       </c>
       <c r="R19" t="n">
-        <v>7122416</v>
+        <v>7122413</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121568900</v>
+        <v>121568903</v>
       </c>
       <c r="B20" t="n">
-        <v>78616</v>
+        <v>56569</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2523,25 +2523,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>761216</v>
+        <v>761213</v>
       </c>
       <c r="R20" t="n">
-        <v>7122302</v>
+        <v>7122424</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2613,7 +2613,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121569157</v>
+        <v>121568907</v>
       </c>
       <c r="B21" t="n">
         <v>78616</v>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>761273</v>
+        <v>761060</v>
       </c>
       <c r="R21" t="n">
-        <v>7122339</v>
+        <v>7122267</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2683,12 +2683,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 32316-2022 artfynd.xlsx
+++ b/artfynd/A 32316-2022 artfynd.xlsx
@@ -1797,7 +1797,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121568906</v>
+        <v>121568904</v>
       </c>
       <c r="B13" t="n">
         <v>78616</v>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>761042</v>
+        <v>761030</v>
       </c>
       <c r="R13" t="n">
-        <v>7122301</v>
+        <v>7122463</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121568900</v>
+        <v>121568903</v>
       </c>
       <c r="B14" t="n">
-        <v>78616</v>
+        <v>56569</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1911,25 +1911,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>761216</v>
+        <v>761213</v>
       </c>
       <c r="R14" t="n">
-        <v>7122302</v>
+        <v>7122424</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2001,7 +2001,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121568902</v>
+        <v>121568905</v>
       </c>
       <c r="B15" t="n">
         <v>78616</v>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>761223</v>
+        <v>761039</v>
       </c>
       <c r="R15" t="n">
-        <v>7122416</v>
+        <v>7122413</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2103,7 +2103,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121568904</v>
+        <v>121568901</v>
       </c>
       <c r="B16" t="n">
         <v>78616</v>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>761030</v>
+        <v>761202</v>
       </c>
       <c r="R16" t="n">
-        <v>7122463</v>
+        <v>7122373</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2205,7 +2205,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121568901</v>
+        <v>121568906</v>
       </c>
       <c r="B17" t="n">
         <v>78616</v>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>761202</v>
+        <v>761042</v>
       </c>
       <c r="R17" t="n">
-        <v>7122373</v>
+        <v>7122301</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2307,7 +2307,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121569157</v>
+        <v>121568907</v>
       </c>
       <c r="B18" t="n">
         <v>78616</v>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>761273</v>
+        <v>761060</v>
       </c>
       <c r="R18" t="n">
-        <v>7122339</v>
+        <v>7122267</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2377,12 +2377,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2409,7 +2409,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121568905</v>
+        <v>121568900</v>
       </c>
       <c r="B19" t="n">
         <v>78616</v>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>761039</v>
+        <v>761216</v>
       </c>
       <c r="R19" t="n">
-        <v>7122413</v>
+        <v>7122302</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121568903</v>
+        <v>121568902</v>
       </c>
       <c r="B20" t="n">
-        <v>56569</v>
+        <v>78616</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2523,25 +2523,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>761213</v>
+        <v>761223</v>
       </c>
       <c r="R20" t="n">
-        <v>7122424</v>
+        <v>7122416</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2613,7 +2613,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121568907</v>
+        <v>121569157</v>
       </c>
       <c r="B21" t="n">
         <v>78616</v>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>761060</v>
+        <v>761273</v>
       </c>
       <c r="R21" t="n">
-        <v>7122267</v>
+        <v>7122339</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2683,12 +2683,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 32316-2022 artfynd.xlsx
+++ b/artfynd/A 32316-2022 artfynd.xlsx
@@ -1797,7 +1797,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121568904</v>
+        <v>121568907</v>
       </c>
       <c r="B13" t="n">
         <v>78616</v>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>761030</v>
+        <v>761060</v>
       </c>
       <c r="R13" t="n">
-        <v>7122463</v>
+        <v>7122267</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121568903</v>
+        <v>121569157</v>
       </c>
       <c r="B14" t="n">
-        <v>56569</v>
+        <v>78616</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1911,25 +1911,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>761213</v>
+        <v>761273</v>
       </c>
       <c r="R14" t="n">
-        <v>7122424</v>
+        <v>7122339</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1969,12 +1969,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2001,7 +2001,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121568905</v>
+        <v>121568900</v>
       </c>
       <c r="B15" t="n">
         <v>78616</v>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>761039</v>
+        <v>761216</v>
       </c>
       <c r="R15" t="n">
-        <v>7122413</v>
+        <v>7122302</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2205,7 +2205,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121568906</v>
+        <v>121568902</v>
       </c>
       <c r="B17" t="n">
         <v>78616</v>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>761042</v>
+        <v>761223</v>
       </c>
       <c r="R17" t="n">
-        <v>7122301</v>
+        <v>7122416</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2307,7 +2307,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121568907</v>
+        <v>121568905</v>
       </c>
       <c r="B18" t="n">
         <v>78616</v>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>761060</v>
+        <v>761039</v>
       </c>
       <c r="R18" t="n">
-        <v>7122267</v>
+        <v>7122413</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2409,7 +2409,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121568900</v>
+        <v>121568904</v>
       </c>
       <c r="B19" t="n">
         <v>78616</v>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>761216</v>
+        <v>761030</v>
       </c>
       <c r="R19" t="n">
-        <v>7122302</v>
+        <v>7122463</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121568902</v>
+        <v>121568903</v>
       </c>
       <c r="B20" t="n">
-        <v>78616</v>
+        <v>56569</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2523,25 +2523,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>761223</v>
+        <v>761213</v>
       </c>
       <c r="R20" t="n">
-        <v>7122416</v>
+        <v>7122424</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2613,7 +2613,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121569157</v>
+        <v>121568906</v>
       </c>
       <c r="B21" t="n">
         <v>78616</v>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>761273</v>
+        <v>761042</v>
       </c>
       <c r="R21" t="n">
-        <v>7122339</v>
+        <v>7122301</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2683,12 +2683,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 32316-2022 artfynd.xlsx
+++ b/artfynd/A 32316-2022 artfynd.xlsx
@@ -1797,7 +1797,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121568907</v>
+        <v>121569157</v>
       </c>
       <c r="B13" t="n">
         <v>78616</v>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>761060</v>
+        <v>761273</v>
       </c>
       <c r="R13" t="n">
-        <v>7122267</v>
+        <v>7122339</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1899,7 +1899,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121569157</v>
+        <v>121568904</v>
       </c>
       <c r="B14" t="n">
         <v>78616</v>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>761273</v>
+        <v>761030</v>
       </c>
       <c r="R14" t="n">
-        <v>7122339</v>
+        <v>7122463</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1969,12 +1969,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121568901</v>
+        <v>121568903</v>
       </c>
       <c r="B16" t="n">
-        <v>78616</v>
+        <v>56569</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2115,25 +2115,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>761202</v>
+        <v>761213</v>
       </c>
       <c r="R16" t="n">
-        <v>7122373</v>
+        <v>7122424</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2307,7 +2307,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121568905</v>
+        <v>121568906</v>
       </c>
       <c r="B18" t="n">
         <v>78616</v>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>761039</v>
+        <v>761042</v>
       </c>
       <c r="R18" t="n">
-        <v>7122413</v>
+        <v>7122301</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2409,7 +2409,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121568904</v>
+        <v>121568907</v>
       </c>
       <c r="B19" t="n">
         <v>78616</v>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>761030</v>
+        <v>761060</v>
       </c>
       <c r="R19" t="n">
-        <v>7122463</v>
+        <v>7122267</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121568903</v>
+        <v>121568901</v>
       </c>
       <c r="B20" t="n">
-        <v>56569</v>
+        <v>78616</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2523,25 +2523,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>761213</v>
+        <v>761202</v>
       </c>
       <c r="R20" t="n">
-        <v>7122424</v>
+        <v>7122373</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2613,7 +2613,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121568906</v>
+        <v>121568905</v>
       </c>
       <c r="B21" t="n">
         <v>78616</v>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>761042</v>
+        <v>761039</v>
       </c>
       <c r="R21" t="n">
-        <v>7122301</v>
+        <v>7122413</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>

--- a/artfynd/A 32316-2022 artfynd.xlsx
+++ b/artfynd/A 32316-2022 artfynd.xlsx
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121569157</v>
+        <v>121568900</v>
       </c>
       <c r="B13" t="n">
-        <v>78616</v>
+        <v>78629</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>761273</v>
+        <v>761216</v>
       </c>
       <c r="R13" t="n">
-        <v>7122339</v>
+        <v>7122302</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1902,7 +1902,7 @@
         <v>121568904</v>
       </c>
       <c r="B14" t="n">
-        <v>78616</v>
+        <v>78629</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121568900</v>
+        <v>121569157</v>
       </c>
       <c r="B15" t="n">
-        <v>78616</v>
+        <v>78629</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>761216</v>
+        <v>761273</v>
       </c>
       <c r="R15" t="n">
-        <v>7122302</v>
+        <v>7122339</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2071,12 +2071,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121568903</v>
+        <v>121568905</v>
       </c>
       <c r="B16" t="n">
-        <v>56569</v>
+        <v>78629</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2115,25 +2115,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>761213</v>
+        <v>761039</v>
       </c>
       <c r="R16" t="n">
-        <v>7122424</v>
+        <v>7122413</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121568902</v>
+        <v>121568907</v>
       </c>
       <c r="B17" t="n">
-        <v>78616</v>
+        <v>78629</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>761223</v>
+        <v>761060</v>
       </c>
       <c r="R17" t="n">
-        <v>7122416</v>
+        <v>7122267</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2307,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121568906</v>
+        <v>121568902</v>
       </c>
       <c r="B18" t="n">
-        <v>78616</v>
+        <v>78629</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>761042</v>
+        <v>761223</v>
       </c>
       <c r="R18" t="n">
-        <v>7122301</v>
+        <v>7122416</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2409,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121568907</v>
+        <v>121568901</v>
       </c>
       <c r="B19" t="n">
-        <v>78616</v>
+        <v>78629</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>761060</v>
+        <v>761202</v>
       </c>
       <c r="R19" t="n">
-        <v>7122267</v>
+        <v>7122373</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121568901</v>
+        <v>121568906</v>
       </c>
       <c r="B20" t="n">
-        <v>78616</v>
+        <v>78629</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>761202</v>
+        <v>761042</v>
       </c>
       <c r="R20" t="n">
-        <v>7122373</v>
+        <v>7122301</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2613,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121568905</v>
+        <v>121568903</v>
       </c>
       <c r="B21" t="n">
-        <v>78616</v>
+        <v>56577</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2625,25 +2625,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>761039</v>
+        <v>761213</v>
       </c>
       <c r="R21" t="n">
-        <v>7122413</v>
+        <v>7122424</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>

--- a/artfynd/A 32316-2022 artfynd.xlsx
+++ b/artfynd/A 32316-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117921682</v>
+        <v>117921681</v>
       </c>
       <c r="B2" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>2059</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>761255</v>
+        <v>761168</v>
       </c>
       <c r="R2" t="n">
-        <v>7122454</v>
+        <v>7122386</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -780,12 +775,7 @@
         <v>117921679</v>
       </c>
       <c r="B3" t="n">
-        <v>91768</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -879,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117921673</v>
+        <v>117921669</v>
       </c>
       <c r="B4" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>760971</v>
+        <v>761245</v>
       </c>
       <c r="R4" t="n">
-        <v>7122339</v>
+        <v>7122347</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,16 +969,11 @@
         <v>117921674</v>
       </c>
       <c r="B5" t="n">
-        <v>91776</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1086,16 +1066,11 @@
         <v>117921672</v>
       </c>
       <c r="B6" t="n">
-        <v>91788</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1185,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117921677</v>
+        <v>117921668</v>
       </c>
       <c r="B7" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92841</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>4745</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>761068</v>
+        <v>761291</v>
       </c>
       <c r="R7" t="n">
-        <v>7122379</v>
+        <v>7122364</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,19 +1257,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117921683</v>
+        <v>117921670</v>
       </c>
       <c r="B8" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1327,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>761278</v>
+        <v>761244</v>
       </c>
       <c r="R8" t="n">
-        <v>7122476</v>
+        <v>7122346</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,37 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117921669</v>
+        <v>117921673</v>
       </c>
       <c r="B9" t="n">
-        <v>91776</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>761245</v>
+        <v>760971</v>
       </c>
       <c r="R9" t="n">
-        <v>7122347</v>
+        <v>7122339</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,16 +1454,11 @@
         <v>117921676</v>
       </c>
       <c r="B10" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1593,19 +1548,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117921684</v>
+        <v>117921677</v>
       </c>
       <c r="B11" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1633,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>761286</v>
+        <v>761068</v>
       </c>
       <c r="R11" t="n">
-        <v>7122485</v>
+        <v>7122379</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,19 +1645,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117921670</v>
+        <v>117921680</v>
       </c>
       <c r="B12" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1735,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>761244</v>
+        <v>761128</v>
       </c>
       <c r="R12" t="n">
-        <v>7122346</v>
+        <v>7122381</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,19 +1742,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121568900</v>
+        <v>117921682</v>
       </c>
       <c r="B13" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1833,17 +1773,17 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gravmark, Vb</t>
+          <t>Kvarnfors, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>761216</v>
+        <v>761255</v>
       </c>
       <c r="R13" t="n">
-        <v>7122302</v>
+        <v>7122454</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1867,12 +1807,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2023-08-30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2023-08-30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1899,19 +1839,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121568904</v>
+        <v>117921683</v>
       </c>
       <c r="B14" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1935,17 +1870,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gravmark, Vb</t>
+          <t>Kvarnfors, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>761030</v>
+        <v>761278</v>
       </c>
       <c r="R14" t="n">
-        <v>7122463</v>
+        <v>7122476</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1969,12 +1904,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2023-08-30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2023-08-30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2001,19 +1936,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121569157</v>
+        <v>117921684</v>
       </c>
       <c r="B15" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2037,17 +1967,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gravmark, Vb</t>
+          <t>Kvarnfors, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>761273</v>
+        <v>761286</v>
       </c>
       <c r="R15" t="n">
-        <v>7122339</v>
+        <v>7122485</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2071,12 +2001,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2023-08-30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2023-08-30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2103,19 +2033,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121568905</v>
+        <v>121568900</v>
       </c>
       <c r="B16" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2143,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>761039</v>
+        <v>761216</v>
       </c>
       <c r="R16" t="n">
-        <v>7122413</v>
+        <v>7122302</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2205,19 +2130,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121568907</v>
+        <v>121568901</v>
       </c>
       <c r="B17" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2245,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>761060</v>
+        <v>761202</v>
       </c>
       <c r="R17" t="n">
-        <v>7122267</v>
+        <v>7122373</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2310,16 +2230,11 @@
         <v>121568902</v>
       </c>
       <c r="B18" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2409,19 +2324,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121568901</v>
+        <v>121568904</v>
       </c>
       <c r="B19" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2449,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>761202</v>
+        <v>761030</v>
       </c>
       <c r="R19" t="n">
-        <v>7122373</v>
+        <v>7122463</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2511,19 +2421,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121568906</v>
+        <v>121568905</v>
       </c>
       <c r="B20" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2551,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>761042</v>
+        <v>761039</v>
       </c>
       <c r="R20" t="n">
-        <v>7122301</v>
+        <v>7122413</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2613,37 +2518,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121568903</v>
+        <v>121568906</v>
       </c>
       <c r="B21" t="n">
-        <v>56577</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2553,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>761213</v>
+        <v>761042</v>
       </c>
       <c r="R21" t="n">
-        <v>7122424</v>
+        <v>7122301</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2712,6 +2612,297 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>121568907</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Gravmark, Vb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>761060</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7122267</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-07-19</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-07-19</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Linda Spjut</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Linda Spjut</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>121569157</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Gravmark, Vb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>761273</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7122339</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-07-03</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-07-03</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Linda Spjut</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Linda Spjut</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>121568903</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Gravmark, Vb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>761213</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7122424</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-07-19</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-07-19</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Linda Spjut</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Linda Spjut</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 32316-2022 artfynd.xlsx
+++ b/artfynd/A 32316-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117921681</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117921679</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117921669</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117921674</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117921672</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117921668</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117921670</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117921673</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117921676</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117921677</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117921680</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117921682</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117921683</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117921684</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121568900</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121568901</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121568902</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121568904</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2515,6 +2610,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121568905</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2612,6 +2712,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121568906</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2709,6 +2814,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121568907</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2806,6 +2916,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121569157</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2903,8 +3018,38 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121568903</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>